--- a/output/pdf_financials_xlsx/UNI.xlsx
+++ b/output/pdf_financials_xlsx/UNI.xlsx
@@ -6151,46 +6151,46 @@
         <v>0.336562</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.478603</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.465974</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.387267</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.440279</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.638231</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.910335</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>1.25161</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>1.688744</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>1.674421</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>1.8562</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>2.250172</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>2.250172</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>2.250172</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>0</v>
+        <v>2.250172</v>
       </c>
     </row>
     <row r="93">
@@ -11162,7 +11162,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -14660,7 +14664,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>-</t>
@@ -19008,7 +19016,11 @@
           <t>Share-­based payment reserve</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/UNI.xlsx
+++ b/output/pdf_financials_xlsx/UNI.xlsx
@@ -1071,10 +1071,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.032186</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.018831</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -2130,10 +2130,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.089366</v>
+        <v>-0.05718</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.064829</v>
+        <v>-0.045998</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>1.804818</v>
@@ -2252,10 +2252,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.089366</v>
+        <v>-0.05718</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.064829</v>
+        <v>-0.045998</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3.524818</v>
@@ -2517,52 +2517,52 @@
         <v>0.554447</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.891658</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.045345</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.125106</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.081402</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.090909</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.205944</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.060828</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.604903</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.212296</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.019973</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.221593</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.275456</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.097261</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.002162</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.791019</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>0.861366</v>
       </c>
     </row>
     <row r="35">
@@ -2639,52 +2639,52 @@
         <v>0.61281</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.035714</v>
+        <v>0.927372</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.022455</v>
+        <v>0.0678</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.125106</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.081402</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.090909</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.205944</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.060828</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.604903</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.212296</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.019973</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.221593</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.275456</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.097261</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.002162</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.791019</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0</v>
+        <v>0.861366</v>
       </c>
     </row>
     <row r="37">
@@ -3371,52 +3371,52 @@
         <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.012362</v>
+        <v>0.120704</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.175633</v>
+        <v>0.130288</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.232732</v>
+        <v>0.107626</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.18502</v>
+        <v>0.103618</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>1.017193</v>
+        <v>0.926284</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>2.015693</v>
+        <v>1.809749</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>2.201537</v>
+        <v>2.140709</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>3.423928</v>
+        <v>2.819025</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>13.913594</v>
+        <v>13.701298</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>4.018849</v>
+        <v>3.998876</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>5.118749</v>
+        <v>4.897156</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>4.470868</v>
+        <v>4.195412</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>2.645705</v>
+        <v>2.548444</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>2.775977</v>
+        <v>2.773815</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>2.66482</v>
+        <v>1.873801</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>2.986733</v>
+        <v>2.125367</v>
       </c>
     </row>
     <row r="49">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -12452,7 +12452,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -55196,7 +55196,7 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">
@@ -56802,7 +56802,7 @@
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E463" t="inlineStr">
@@ -58464,7 +58464,7 @@
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
@@ -59914,7 +59914,7 @@
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
@@ -62034,7 +62034,7 @@
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E513" t="inlineStr">
@@ -63286,7 +63286,7 @@
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E525" t="inlineStr">
@@ -64646,7 +64646,7 @@
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E538" t="inlineStr">
@@ -66126,7 +66126,7 @@
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E552" t="inlineStr">
@@ -71450,7 +71450,7 @@
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E603" t="inlineStr">
@@ -73050,7 +73050,7 @@
       </c>
       <c r="D618" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E618" t="inlineStr">
@@ -74434,7 +74434,7 @@
       </c>
       <c r="D631" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E631" s="5" t="n">

--- a/output/pdf_financials_xlsx/UNI.xlsx
+++ b/output/pdf_financials_xlsx/UNI.xlsx
@@ -2200,13 +2200,13 @@
         <v>1.72</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>2.440584</v>
+        <v>2.531151</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.638416</v>
+        <v>0.729867</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>0.09214799999999999</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>0.186156</v>
@@ -2261,13 +2261,13 @@
         <v>3.524818</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>5.091416</v>
+        <v>5.181983</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>4.580426</v>
+        <v>4.671877</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>2.739468</v>
+        <v>2.831616</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>0.6588000000000001</v>
@@ -2326,13 +2326,13 @@
         <v>31.51573946001139</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>18.99750545186843</v>
+        <v>19.33543640786562</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>15.75682178548848</v>
+        <v>16.07141634702156</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>9.975216967599847</v>
+        <v>10.31075521558463</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>2.954519901951916</v>
@@ -6583,16 +6583,16 @@
         <v>0</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>2.531151</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.729867</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.09214799999999999</v>
       </c>
       <c r="H100" s="3" t="n">
         <v>0.186156</v>
@@ -7318,10 +7318,10 @@
         <v>0</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.0025</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>0.0036</v>
       </c>
       <c r="G112" s="3" t="n">
         <v>0</v>
@@ -46666,7 +46666,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D366" t="inlineStr"/>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E366" t="inlineStr">
         <is>
           <t>-</t>
@@ -47808,7 +47812,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D377" t="inlineStr"/>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E377" t="inlineStr">
         <is>
           <t>-</t>
@@ -48116,7 +48124,7 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
@@ -48426,7 +48434,11 @@
           <t>Proceeds on disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D383" t="inlineStr"/>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E383" t="inlineStr">
         <is>
           <t>-</t>
@@ -49258,7 +49270,7 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
@@ -50418,7 +50430,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">

--- a/output/pdf_financials_xlsx/UNI.xlsx
+++ b/output/pdf_financials_xlsx/UNI.xlsx
@@ -7443,7 +7443,7 @@
         <v>0</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>0</v>
+        <v>-1.205488</v>
       </c>
       <c r="G114" s="3" t="n">
         <v>0</v>
@@ -7495,7 +7495,7 @@
         <v>0</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>0.656043</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>0</v>
@@ -7510,7 +7510,7 @@
         <v>0</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>0.01223</v>
       </c>
       <c r="I115" s="3" t="n">
         <v>0</v>
@@ -7574,34 +7574,34 @@
         <v>0</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>0</v>
+        <v>-1.125055</v>
       </c>
       <c r="J116" s="3" t="n">
-        <v>0</v>
+        <v>-0.32267</v>
       </c>
       <c r="K116" s="3" t="n">
-        <v>0</v>
+        <v>-0.54498</v>
       </c>
       <c r="L116" s="3" t="n">
-        <v>0</v>
+        <v>-0.27733</v>
       </c>
       <c r="M116" s="3" t="n">
-        <v>0</v>
+        <v>-1.635366</v>
       </c>
       <c r="N116" s="3" t="n">
-        <v>0</v>
+        <v>-0.74605</v>
       </c>
       <c r="O116" s="3" t="n">
-        <v>0</v>
+        <v>-0.969854</v>
       </c>
       <c r="P116" s="3" t="n">
-        <v>0</v>
+        <v>-0.443697</v>
       </c>
       <c r="Q116" s="3" t="n">
-        <v>0</v>
+        <v>-0.334102</v>
       </c>
       <c r="R116" s="3" t="n">
-        <v>0</v>
+        <v>-0.01367</v>
       </c>
       <c r="S116" s="3" t="n">
         <v>0</v>
@@ -29746,7 +29746,11 @@
           <t>Purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr"/>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E203" t="inlineStr">
         <is>
           <t>-</t>
@@ -34984,7 +34988,11 @@
           <t>Purchase of intangible assets (Note 9)</t>
         </is>
       </c>
-      <c r="D253" t="inlineStr"/>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E253" t="inlineStr">
         <is>
           <t>-</t>
@@ -36794,7 +36802,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D271" t="inlineStr"/>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E271" t="inlineStr">
         <is>
           <t>-</t>
@@ -38960,7 +38972,11 @@
           <t>Purchase of intangible assets (Note 8)</t>
         </is>
       </c>
-      <c r="D292" t="inlineStr"/>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E292" t="inlineStr">
         <is>
           <t>-</t>
@@ -40604,7 +40620,11 @@
           <t>Purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D308" t="inlineStr"/>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E308" t="inlineStr">
         <is>
           <t>-</t>
@@ -44998,7 +45018,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D350" t="inlineStr"/>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E350" t="inlineStr">
         <is>
           <t>-</t>
@@ -48542,7 +48566,11 @@
           <t>Acquisition of investment (Note 6)</t>
         </is>
       </c>
-      <c r="D384" t="inlineStr"/>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E384" t="inlineStr">
         <is>
           <t>-</t>
@@ -49060,7 +49088,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D389" t="inlineStr"/>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E389" t="inlineStr">
         <is>
           <t>-</t>
@@ -49906,7 +49938,11 @@
           <t>Acquisition of investment (Note 7)</t>
         </is>
       </c>
-      <c r="D397" t="inlineStr"/>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E397" t="inlineStr">
         <is>
           <t>-</t>
@@ -50222,7 +50258,11 @@
           <t>Future income taxes</t>
         </is>
       </c>
-      <c r="D400" t="inlineStr"/>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E400" t="inlineStr">
         <is>
           <t>-</t>
@@ -51276,7 +51316,11 @@
           <t>Proceeds on share issuance (Note 7 (b))</t>
         </is>
       </c>
-      <c r="D410" t="inlineStr"/>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E410" t="inlineStr">
         <is>
           <t>-</t>
@@ -52976,7 +53020,11 @@
           <t>Proceeds on share issuance (Note 8 (b))</t>
         </is>
       </c>
-      <c r="D426" t="inlineStr"/>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E426" t="inlineStr">
         <is>
           <t>-</t>
@@ -53082,7 +53130,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D427" t="inlineStr"/>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E427" t="inlineStr">
         <is>
           <t>-</t>
@@ -54150,7 +54202,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D437" t="inlineStr"/>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E437" t="inlineStr">
         <is>
           <t>-</t>
@@ -57222,7 +57278,11 @@
           <t>Income tax recovery (Note 16)</t>
         </is>
       </c>
-      <c r="D467" t="inlineStr"/>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E467" t="inlineStr">
         <is>
           <t>-</t>
@@ -65188,7 +65248,11 @@
           <t>Income tax (recovery) expense (Note 17)</t>
         </is>
       </c>
-      <c r="D543" t="inlineStr"/>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E543" t="inlineStr">
         <is>
           <t>-</t>
